--- a/Models/Птицы/results/Птица - Результаты прогнозов ХВ средние.xlsx
+++ b/Models/Птицы/results/Птица - Результаты прогнозов ХВ средние.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1217.82</v>
+        <v>1670.51</v>
       </c>
       <c r="C2" t="n">
-        <v>986.42</v>
+        <v>1445.79</v>
       </c>
       <c r="D2" t="n">
-        <v>9.369999999999999</v>
+        <v>13.02</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36.64</v>
+        <v>34.03</v>
       </c>
       <c r="C3" t="n">
-        <v>30.45</v>
+        <v>26.98</v>
       </c>
       <c r="D3" t="n">
-        <v>384.26</v>
+        <v>277.84</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>885.29</v>
+        <v>1183.86</v>
       </c>
       <c r="C4" t="n">
-        <v>773.67</v>
+        <v>1044.2</v>
       </c>
       <c r="D4" t="n">
-        <v>6.56</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="5">
@@ -505,10 +505,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="C5" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="D5" t="inlineStr"/>
     </row>
@@ -519,13 +519,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>571.62</v>
+        <v>569.14</v>
       </c>
       <c r="C6" t="n">
-        <v>515.9</v>
+        <v>522.48</v>
       </c>
       <c r="D6" t="n">
-        <v>8.359999999999999</v>
+        <v>8.550000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -541,7 +541,7 @@
         <v>0.06</v>
       </c>
       <c r="D7" t="n">
-        <v>54.28</v>
+        <v>56.93</v>
       </c>
     </row>
     <row r="8">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D8" t="inlineStr"/>
     </row>
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>40.75</v>
+        <v>8.77</v>
       </c>
       <c r="C9" t="n">
-        <v>34.22</v>
+        <v>7.97</v>
       </c>
       <c r="D9" t="n">
-        <v>423.8</v>
+        <v>168.34</v>
       </c>
     </row>
     <row r="10">
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>338.56</v>
+        <v>584.1799999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>294.65</v>
+        <v>511.77</v>
       </c>
       <c r="D10" t="n">
-        <v>17.5</v>
+        <v>25.54</v>
       </c>
     </row>
     <row r="11">
@@ -597,13 +597,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>204.4</v>
+        <v>265.84</v>
       </c>
       <c r="C11" t="n">
-        <v>166.59</v>
+        <v>214.58</v>
       </c>
       <c r="D11" t="n">
-        <v>16.21</v>
+        <v>20.69</v>
       </c>
     </row>
     <row r="12">
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>117.63</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="C12" t="n">
-        <v>104.95</v>
+        <v>80.45</v>
       </c>
       <c r="D12" t="n">
-        <v>10.48</v>
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -629,13 +629,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>301.36</v>
+        <v>275.32</v>
       </c>
       <c r="C13" t="n">
-        <v>266.31</v>
+        <v>247</v>
       </c>
       <c r="D13" t="n">
-        <v>27.36</v>
+        <v>18.29</v>
       </c>
     </row>
     <row r="14">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8.92</v>
+        <v>8.09</v>
       </c>
       <c r="C14" t="n">
-        <v>6.77</v>
+        <v>6.08</v>
       </c>
       <c r="D14" t="n">
-        <v>98.45999999999999</v>
+        <v>207.49</v>
       </c>
     </row>
     <row r="15">
@@ -661,13 +661,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>289.2</v>
+        <v>356.1</v>
       </c>
       <c r="C15" t="n">
-        <v>257.3</v>
+        <v>307.53</v>
       </c>
       <c r="D15" t="n">
-        <v>42.42</v>
+        <v>49.15</v>
       </c>
     </row>
     <row r="16">
@@ -677,13 +677,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>109.29</v>
+        <v>163.87</v>
       </c>
       <c r="C16" t="n">
-        <v>96.93000000000001</v>
+        <v>149.35</v>
       </c>
       <c r="D16" t="n">
-        <v>5.13</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="17">
@@ -693,13 +693,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>94.16</v>
+        <v>83.77</v>
       </c>
       <c r="C17" t="n">
-        <v>74.88</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>181.16</v>
+        <v>121.22</v>
       </c>
     </row>
     <row r="18">
@@ -709,10 +709,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.71</v>
+        <v>2.09</v>
       </c>
       <c r="C18" t="n">
-        <v>4.34</v>
+        <v>1.75</v>
       </c>
       <c r="D18" t="inlineStr"/>
     </row>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>114.79</v>
+        <v>177.39</v>
       </c>
       <c r="C19" t="n">
-        <v>103.49</v>
+        <v>157.48</v>
       </c>
       <c r="D19" t="n">
-        <v>45.92</v>
+        <v>38.39</v>
       </c>
     </row>
     <row r="20">
@@ -739,13 +739,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>158.09</v>
+        <v>266.32</v>
       </c>
       <c r="C20" t="n">
-        <v>145.42</v>
+        <v>256.75</v>
       </c>
       <c r="D20" t="n">
-        <v>96.06999999999999</v>
+        <v>44.78</v>
       </c>
     </row>
     <row r="21">
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>389.11</v>
+        <v>210.68</v>
       </c>
       <c r="C21" t="n">
-        <v>359.01</v>
+        <v>172.47</v>
       </c>
       <c r="D21" t="n">
-        <v>74.15000000000001</v>
+        <v>24.55</v>
       </c>
     </row>
   </sheetData>
